--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122801458</v>
+        <v>122801651</v>
       </c>
       <c r="B3" t="n">
-        <v>57428</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +837,11 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122801651</v>
+        <v>122801458</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>57428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +923,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,11 +947,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122801651</v>
+        <v>122801458</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,11 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122801458</v>
+        <v>122801651</v>
       </c>
       <c r="B4" t="n">
-        <v>57428</v>
+        <v>57484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +943,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122801458</v>
       </c>
       <c r="B3" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>122801651</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122801458</v>
+        <v>122801651</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102621</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +837,11 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -907,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122801651</v>
+        <v>122801458</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,20 +923,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,11 +947,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 22367-2023 artfynd.xlsx
+++ b/artfynd/A 22367-2023 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122801651</v>
+        <v>122801458</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,11 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122801458</v>
+        <v>122801651</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,20 +919,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -947,7 +943,11 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
